--- a/public/kit-shopping-guide.xlsx
+++ b/public/kit-shopping-guide.xlsx
@@ -572,8 +572,10 @@
           <t>SC1632</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>12000</v>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>~9,900원</t>
+        </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -595,8 +597,10 @@
           <t>103100142</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>5500</v>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>~5,500원</t>
+        </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -618,8 +622,10 @@
           <t>103020272</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>2700</v>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>~2,200원</t>
+        </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -641,8 +647,10 @@
           <t>110990210</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>3500</v>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>~2,200원</t>
+        </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -664,8 +672,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>3000</v>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>~3,000원</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -684,6 +694,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
@@ -742,94 +753,116 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>코스A 1막만</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>26700</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>21800</v>
-      </c>
-      <c r="D2" s="6">
-        <f>B2+C2</f>
-        <v/>
+          <t>코스 A 1막만</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>~23,000원</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>A, B, C (~21,300원)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>~44,300원</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>코스A 전체 (1~3막)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>26700</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>101500</v>
-      </c>
-      <c r="D3" s="6">
-        <f>B3+C3</f>
-        <v/>
+          <t>코스 A 전체 (1~3막)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>~23,000원</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>A~H (~169,900원)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>~192,900원</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>코스B Lv.1만</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>26700</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>28400</v>
-      </c>
-      <c r="D4" s="6">
-        <f>B4+C4</f>
-        <v/>
+          <t>코스 B Lv.1만</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>~23,000원</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>A, B, I, C (~26,200원)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>~49,200원</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>코스B 전체 (Lv.1~4)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>26700</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>96100</v>
-      </c>
-      <c r="D5" s="6">
-        <f>B5+C5</f>
-        <v/>
+          <t>코스 B 전체 (Lv.1~4)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>~23,000원</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>A~D, I, J, K (~158,600원)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>~181,600원</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>코스A+B 올인원</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>26700</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>120100</v>
-      </c>
-      <c r="D6" s="13">
-        <f>B6+C6</f>
-        <v/>
-      </c>
-    </row>
+          <t>코스 A + B 올인원</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>~23,000원</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>A~K (~192,300원)</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>~215,300원</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>가격 기준일: 2026.03.15. 디바이스마트 및 Seeed Studio 참고가</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1504,7 +1537,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0x38</t>
+          <t>~7,900원</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
@@ -1542,7 +1575,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>~5,200원</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -1580,7 +1613,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0x3C</t>
+          <t>~8,200원</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -1618,7 +1651,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0x62</t>
+          <t>~114,900원</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
@@ -1656,7 +1689,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>~21,000원</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -1694,7 +1727,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>~4,900원</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -1732,7 +1765,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>~2,100원</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -1770,7 +1803,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>~5,700원</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -1808,7 +1841,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>~4,900원</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
@@ -1846,7 +1879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0x68</t>
+          <t>~3,500원</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
@@ -1882,7 +1915,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>~14,000원</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
@@ -1902,6 +1935,7 @@
         <v>11.9</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
